--- a/frontend/Ragnarok_default/src/lib/workbook/__fixtures__/backend_project.xlsx
+++ b/frontend/Ragnarok_default/src/lib/workbook/__fixtures__/backend_project.xlsx
@@ -16,6 +16,7 @@
     <sheet name="RAGNAROK_Constraints" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="RAGNAROK_RunState" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="RAGNAROK_Settings" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="RAGNAROK_Bundle" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -461,6 +462,42 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>part</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>json</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>{"model": {"buses": [{"name": "n1", "v_nom": 380.0}, {"name": "n2", "v_nom": 380.0}], "generators": [{"name": "wind", "bus": "n1", "p_nom": 100.0, "carrier": "wind", "p_nom_opt": 999.0}, {"name": "gas", "bus": "n2", "p_nom": 50.0, "carrier": "gas", "marginal_cost": 40.0}], "loads": [{"name": "load1", "bus": "n1", "p_set": ""}], "generators-p_max_pu": [{"snapshot": "2025-01-01T00:00:00", "wind": 0.8}, {"snapshot": "2025-01-01T01:00:00", "wind": 0.6}], "lines": []}, "scenario": {"discountRate": 0.07, "carbonPrice": 50.0, "constraints": [{"id": "c1", "enabled": true, "label": "CO2", "metric": "co2_cap", "carrier": "", "value": 1000.0, "unit": "t"}]}, "options": {"snapshotStart": 0, "snapshotEnd": 2, "snapshotWeight": 1, "currencySymbol": "$", "dateFormat": "auto", "filename": "demo.xlsx"}, "result": {"outputs": {"static": {"generators": {"wind": {"p_nom_opt": 120.0}, "gas": {"p_nom_opt": 50.0}}}, "series": {"generators-p": [{"snapshot": "2025-01-01T00:00:00", "wind": 80.0, "gas": 10.0}, {"snapshot": "2025-01-01T01:00:00", "wind": 60.0, "gas": 30.0}]}}, "runMeta": {"componentCounts": {"generators": 2, "buses": 2}}, "pathway": {"enabled": false}, "rolling": {"enabled": false}, "narrative": ["Solved in 2 snapshots."]}}</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/frontend/Ragnarok_default/src/lib/workbook/__fixtures__/backend_project.xlsx
+++ b/frontend/Ragnarok_default/src/lib/workbook/__fixtures__/backend_project.xlsx
@@ -16,7 +16,6 @@
     <sheet name="RAGNAROK_Constraints" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="RAGNAROK_RunState" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="RAGNAROK_Settings" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="RAGNAROK_Bundle" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -462,42 +461,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>part</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>json</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>0</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>{"model": {"buses": [{"name": "n1", "v_nom": 380.0}, {"name": "n2", "v_nom": 380.0}], "generators": [{"name": "wind", "bus": "n1", "p_nom": 100.0, "carrier": "wind", "p_nom_opt": 999.0}, {"name": "gas", "bus": "n2", "p_nom": 50.0, "carrier": "gas", "marginal_cost": 40.0}], "loads": [{"name": "load1", "bus": "n1", "p_set": ""}], "generators-p_max_pu": [{"snapshot": "2025-01-01T00:00:00", "wind": 0.8}, {"snapshot": "2025-01-01T01:00:00", "wind": 0.6}], "lines": []}, "scenario": {"discountRate": 0.07, "carbonPrice": 50.0, "constraints": [{"id": "c1", "enabled": true, "label": "CO2", "metric": "co2_cap", "carrier": "", "value": 1000.0, "unit": "t"}]}, "options": {"snapshotStart": 0, "snapshotEnd": 2, "snapshotWeight": 1, "currencySymbol": "$", "dateFormat": "auto", "filename": "demo.xlsx"}, "result": {"outputs": {"static": {"generators": {"wind": {"p_nom_opt": 120.0}, "gas": {"p_nom_opt": 50.0}}}, "series": {"generators-p": [{"snapshot": "2025-01-01T00:00:00", "wind": 80.0, "gas": 10.0}, {"snapshot": "2025-01-01T01:00:00", "wind": 60.0, "gas": 30.0}]}}, "runMeta": {"componentCounts": {"generators": 2, "buses": 2}}, "pathway": {"enabled": false}, "rolling": {"enabled": false}, "narrative": ["Solved in 2 snapshots."]}}</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
